--- a/docs/Contactor_IQC_Sheet_Template.xlsx
+++ b/docs/Contactor_IQC_Sheet_Template.xlsx
@@ -768,10 +768,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -780,9 +781,15 @@
           <t>Operator Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Max 10 names, one per row from A2. Shown in the login dropdown.</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Operator Password</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Max 10 operators. Password is checked on the login screen; leave it empty for no password.</t>
         </is>
       </c>
     </row>
@@ -792,6 +799,11 @@
           <t>Operator 1</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>password 1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -799,11 +811,21 @@
           <t>Operator 2</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>password 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>Operator 3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>password 3</t>
         </is>
       </c>
     </row>
@@ -980,9 +1002,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -993,7 +1013,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Operators  : names shown in the login dropdown (max 10).</t>
+          <t>Operators  : names (column A) and passwords (column B) for the login screen, max 10.</t>
         </is>
       </c>
     </row>
@@ -1004,9 +1024,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1056,9 +1074,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>

--- a/docs/Contactor_IQC_Sheet_Template.xlsx
+++ b/docs/Contactor_IQC_Sheet_Template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,13 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFCC00"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,9 @@
       <patternFill patternType="solid">
         <fgColor rgb="000F1115"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
     </fill>
   </fills>
   <borders count="1">
@@ -69,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -80,6 +88,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,62 +498,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Inrush LSL (A)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Inrush USL (A)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Cont LSL (A)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Cont USL (A)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Inrush Window (ms)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Settle (ms)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Avg Window (ms)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Release (ms)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Cycles</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Cycle Gap (ms)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Stagger (ms)</t>
         </is>
@@ -776,12 +788,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Operator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Operator Password</t>
         </is>
@@ -840,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:BZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -849,134 +861,484 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
+    <col width="11" customWidth="1" min="51" max="51"/>
+    <col width="11" customWidth="1" min="52" max="52"/>
+    <col width="11" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="11" customWidth="1" min="57" max="57"/>
+    <col width="11" customWidth="1" min="58" max="58"/>
+    <col width="11" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="60" max="60"/>
+    <col width="11" customWidth="1" min="61" max="61"/>
+    <col width="11" customWidth="1" min="62" max="62"/>
+    <col width="11" customWidth="1" min="63" max="63"/>
+    <col width="11" customWidth="1" min="64" max="64"/>
+    <col width="11" customWidth="1" min="65" max="65"/>
+    <col width="11" customWidth="1" min="66" max="66"/>
+    <col width="11" customWidth="1" min="67" max="67"/>
+    <col width="11" customWidth="1" min="68" max="68"/>
+    <col width="11" customWidth="1" min="69" max="69"/>
+    <col width="11" customWidth="1" min="70" max="70"/>
+    <col width="11" customWidth="1" min="71" max="71"/>
+    <col width="11" customWidth="1" min="72" max="72"/>
+    <col width="11" customWidth="1" min="73" max="73"/>
+    <col width="11" customWidth="1" min="74" max="74"/>
+    <col width="11" customWidth="1" min="75" max="75"/>
+    <col width="11" customWidth="1" min="76" max="76"/>
+    <col width="11" customWidth="1" min="77" max="77"/>
+    <col width="11" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Serial</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cycle</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cycle Result</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Inrush (A)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Inrush P/F</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Cont (A)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Cont P/F</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Continuity</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Fail Step</t>
         </is>
       </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>1- Open</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>1- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>1- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>1- Cont (A)</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>1- Cont P/F</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>1- Continuity</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>1- Release</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>2- Open</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>2- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>2- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>2- Cont (A)</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>2- Cont P/F</t>
+        </is>
+      </c>
+      <c r="U1" s="6" t="inlineStr">
+        <is>
+          <t>2- Continuity</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
+          <t>2- Release</t>
+        </is>
+      </c>
+      <c r="W1" s="6" t="inlineStr">
+        <is>
+          <t>3- Open</t>
+        </is>
+      </c>
+      <c r="X1" s="6" t="inlineStr">
+        <is>
+          <t>3- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="Y1" s="6" t="inlineStr">
+        <is>
+          <t>3- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="Z1" s="6" t="inlineStr">
+        <is>
+          <t>3- Cont (A)</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>3- Cont P/F</t>
+        </is>
+      </c>
+      <c r="AB1" s="6" t="inlineStr">
+        <is>
+          <t>3- Continuity</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>3- Release</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>4- Open</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>4- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="AF1" s="6" t="inlineStr">
+        <is>
+          <t>4- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>4- Cont (A)</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>4- Cont P/F</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
+        <is>
+          <t>4- Continuity</t>
+        </is>
+      </c>
+      <c r="AJ1" s="6" t="inlineStr">
+        <is>
+          <t>4- Release</t>
+        </is>
+      </c>
+      <c r="AK1" s="6" t="inlineStr">
+        <is>
+          <t>5- Open</t>
+        </is>
+      </c>
+      <c r="AL1" s="6" t="inlineStr">
+        <is>
+          <t>5- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="AM1" s="6" t="inlineStr">
+        <is>
+          <t>5- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="AN1" s="6" t="inlineStr">
+        <is>
+          <t>5- Cont (A)</t>
+        </is>
+      </c>
+      <c r="AO1" s="6" t="inlineStr">
+        <is>
+          <t>5- Cont P/F</t>
+        </is>
+      </c>
+      <c r="AP1" s="6" t="inlineStr">
+        <is>
+          <t>5- Continuity</t>
+        </is>
+      </c>
+      <c r="AQ1" s="6" t="inlineStr">
+        <is>
+          <t>5- Release</t>
+        </is>
+      </c>
+      <c r="AR1" s="6" t="inlineStr">
+        <is>
+          <t>6- Open</t>
+        </is>
+      </c>
+      <c r="AS1" s="6" t="inlineStr">
+        <is>
+          <t>6- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="AT1" s="6" t="inlineStr">
+        <is>
+          <t>6- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="AU1" s="6" t="inlineStr">
+        <is>
+          <t>6- Cont (A)</t>
+        </is>
+      </c>
+      <c r="AV1" s="6" t="inlineStr">
+        <is>
+          <t>6- Cont P/F</t>
+        </is>
+      </c>
+      <c r="AW1" s="6" t="inlineStr">
+        <is>
+          <t>6- Continuity</t>
+        </is>
+      </c>
+      <c r="AX1" s="6" t="inlineStr">
+        <is>
+          <t>6- Release</t>
+        </is>
+      </c>
+      <c r="AY1" s="6" t="inlineStr">
+        <is>
+          <t>7- Open</t>
+        </is>
+      </c>
+      <c r="AZ1" s="6" t="inlineStr">
+        <is>
+          <t>7- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="BA1" s="6" t="inlineStr">
+        <is>
+          <t>7- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="BB1" s="6" t="inlineStr">
+        <is>
+          <t>7- Cont (A)</t>
+        </is>
+      </c>
+      <c r="BC1" s="6" t="inlineStr">
+        <is>
+          <t>7- Cont P/F</t>
+        </is>
+      </c>
+      <c r="BD1" s="6" t="inlineStr">
+        <is>
+          <t>7- Continuity</t>
+        </is>
+      </c>
+      <c r="BE1" s="6" t="inlineStr">
+        <is>
+          <t>7- Release</t>
+        </is>
+      </c>
+      <c r="BF1" s="6" t="inlineStr">
+        <is>
+          <t>8- Open</t>
+        </is>
+      </c>
+      <c r="BG1" s="6" t="inlineStr">
+        <is>
+          <t>8- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="BH1" s="6" t="inlineStr">
+        <is>
+          <t>8- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="BI1" s="6" t="inlineStr">
+        <is>
+          <t>8- Cont (A)</t>
+        </is>
+      </c>
+      <c r="BJ1" s="6" t="inlineStr">
+        <is>
+          <t>8- Cont P/F</t>
+        </is>
+      </c>
+      <c r="BK1" s="6" t="inlineStr">
+        <is>
+          <t>8- Continuity</t>
+        </is>
+      </c>
+      <c r="BL1" s="6" t="inlineStr">
+        <is>
+          <t>8- Release</t>
+        </is>
+      </c>
+      <c r="BM1" s="6" t="inlineStr">
+        <is>
+          <t>9- Open</t>
+        </is>
+      </c>
+      <c r="BN1" s="6" t="inlineStr">
+        <is>
+          <t>9- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="BO1" s="6" t="inlineStr">
+        <is>
+          <t>9- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="BP1" s="6" t="inlineStr">
+        <is>
+          <t>9- Cont (A)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="6" t="inlineStr">
+        <is>
+          <t>9- Cont P/F</t>
+        </is>
+      </c>
+      <c r="BR1" s="6" t="inlineStr">
+        <is>
+          <t>9- Continuity</t>
+        </is>
+      </c>
+      <c r="BS1" s="6" t="inlineStr">
+        <is>
+          <t>9- Release</t>
+        </is>
+      </c>
+      <c r="BT1" s="6" t="inlineStr">
+        <is>
+          <t>10- Open</t>
+        </is>
+      </c>
+      <c r="BU1" s="6" t="inlineStr">
+        <is>
+          <t>10- Inrush (A)</t>
+        </is>
+      </c>
+      <c r="BV1" s="6" t="inlineStr">
+        <is>
+          <t>10- Inrush P/F</t>
+        </is>
+      </c>
+      <c r="BW1" s="6" t="inlineStr">
+        <is>
+          <t>10- Cont (A)</t>
+        </is>
+      </c>
+      <c r="BX1" s="6" t="inlineStr">
+        <is>
+          <t>10- Cont P/F</t>
+        </is>
+      </c>
+      <c r="BY1" s="6" t="inlineStr">
+        <is>
+          <t>10- Continuity</t>
+        </is>
+      </c>
+      <c r="BZ1" s="6" t="inlineStr">
+        <is>
+          <t>10- Release</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H100000">
+  <conditionalFormatting sqref="G2:BZ100000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G100000">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"ABORTED"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I100000">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
-      <formula>"FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K100000">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
-      <formula>"FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:O100000">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
-      <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -989,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1002,81 +1364,101 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Specs      : limits and timings per model. The rig downloads this at boot and when SYNC NOW is pressed.</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Specs      : limits and timings per model. Read by the rig at boot and on SYNC NOW.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Operators  : names (column A) and passwords (column B) for the login screen, max 10.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Results    : the rig appends one row per channel per cycle. Do not type in this tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Results    : ONE ROW PER CONTACTOR, written by the rig. Do not type in this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Results columns:</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S.No        row number (filled by the rig as =ROW()-1)</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S.No         row number (=ROW()-1)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Timestamp   test time from Google's clock; a * at the end means the rig was offline and this is the upload time</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Timestamp    when the unit finished (IST). A * at the end = the rig was offline; this is the upload time.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cycle       e.g. 3/5</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Channel      rig slot CH1..CH5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cycle Result PASS / FAIL / ABORTED</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Overall      PASS (all cycles passed) / FAIL / ABORTED (STOP ALL)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -NA-        step not tested (stopped at an earlier failure or aborted)</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fail Step    step that failed, e.g. In-rush, Continuous current, Continuity, Release, Open</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NA          measured but not judged (model has no limit for it)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  n- ...       results of cycle n (Open, Inrush A, Inrush P/F, Cont A, Cont P/F, Continuity, Release)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -NA-         not tested (stopped at an earlier failure, or cycle never run)</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NA           measured but not judged (the model has no limit for it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Do not rename the tabs or edit the header rows - the firmware looks them up by name.</t>
         </is>

--- a/docs/Contactor_IQC_Sheet_Template.xlsx
+++ b/docs/Contactor_IQC_Sheet_Template.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -766,6 +766,13 @@
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Stagger = delay between the start of consecutive channels (keeps in-rush currents from overlapping).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cycles: 1 to 5 (the Results tab has columns for 5 cycles).</t>
         </is>
       </c>
     </row>
@@ -852,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ1"/>
+  <dimension ref="A1:AQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1151,181 +1158,6 @@
           <t>5- Release</t>
         </is>
       </c>
-      <c r="AR1" s="6" t="inlineStr">
-        <is>
-          <t>6- Open</t>
-        </is>
-      </c>
-      <c r="AS1" s="6" t="inlineStr">
-        <is>
-          <t>6- Inrush (A)</t>
-        </is>
-      </c>
-      <c r="AT1" s="6" t="inlineStr">
-        <is>
-          <t>6- Inrush P/F</t>
-        </is>
-      </c>
-      <c r="AU1" s="6" t="inlineStr">
-        <is>
-          <t>6- Cont (A)</t>
-        </is>
-      </c>
-      <c r="AV1" s="6" t="inlineStr">
-        <is>
-          <t>6- Cont P/F</t>
-        </is>
-      </c>
-      <c r="AW1" s="6" t="inlineStr">
-        <is>
-          <t>6- Continuity</t>
-        </is>
-      </c>
-      <c r="AX1" s="6" t="inlineStr">
-        <is>
-          <t>6- Release</t>
-        </is>
-      </c>
-      <c r="AY1" s="6" t="inlineStr">
-        <is>
-          <t>7- Open</t>
-        </is>
-      </c>
-      <c r="AZ1" s="6" t="inlineStr">
-        <is>
-          <t>7- Inrush (A)</t>
-        </is>
-      </c>
-      <c r="BA1" s="6" t="inlineStr">
-        <is>
-          <t>7- Inrush P/F</t>
-        </is>
-      </c>
-      <c r="BB1" s="6" t="inlineStr">
-        <is>
-          <t>7- Cont (A)</t>
-        </is>
-      </c>
-      <c r="BC1" s="6" t="inlineStr">
-        <is>
-          <t>7- Cont P/F</t>
-        </is>
-      </c>
-      <c r="BD1" s="6" t="inlineStr">
-        <is>
-          <t>7- Continuity</t>
-        </is>
-      </c>
-      <c r="BE1" s="6" t="inlineStr">
-        <is>
-          <t>7- Release</t>
-        </is>
-      </c>
-      <c r="BF1" s="6" t="inlineStr">
-        <is>
-          <t>8- Open</t>
-        </is>
-      </c>
-      <c r="BG1" s="6" t="inlineStr">
-        <is>
-          <t>8- Inrush (A)</t>
-        </is>
-      </c>
-      <c r="BH1" s="6" t="inlineStr">
-        <is>
-          <t>8- Inrush P/F</t>
-        </is>
-      </c>
-      <c r="BI1" s="6" t="inlineStr">
-        <is>
-          <t>8- Cont (A)</t>
-        </is>
-      </c>
-      <c r="BJ1" s="6" t="inlineStr">
-        <is>
-          <t>8- Cont P/F</t>
-        </is>
-      </c>
-      <c r="BK1" s="6" t="inlineStr">
-        <is>
-          <t>8- Continuity</t>
-        </is>
-      </c>
-      <c r="BL1" s="6" t="inlineStr">
-        <is>
-          <t>8- Release</t>
-        </is>
-      </c>
-      <c r="BM1" s="6" t="inlineStr">
-        <is>
-          <t>9- Open</t>
-        </is>
-      </c>
-      <c r="BN1" s="6" t="inlineStr">
-        <is>
-          <t>9- Inrush (A)</t>
-        </is>
-      </c>
-      <c r="BO1" s="6" t="inlineStr">
-        <is>
-          <t>9- Inrush P/F</t>
-        </is>
-      </c>
-      <c r="BP1" s="6" t="inlineStr">
-        <is>
-          <t>9- Cont (A)</t>
-        </is>
-      </c>
-      <c r="BQ1" s="6" t="inlineStr">
-        <is>
-          <t>9- Cont P/F</t>
-        </is>
-      </c>
-      <c r="BR1" s="6" t="inlineStr">
-        <is>
-          <t>9- Continuity</t>
-        </is>
-      </c>
-      <c r="BS1" s="6" t="inlineStr">
-        <is>
-          <t>9- Release</t>
-        </is>
-      </c>
-      <c r="BT1" s="6" t="inlineStr">
-        <is>
-          <t>10- Open</t>
-        </is>
-      </c>
-      <c r="BU1" s="6" t="inlineStr">
-        <is>
-          <t>10- Inrush (A)</t>
-        </is>
-      </c>
-      <c r="BV1" s="6" t="inlineStr">
-        <is>
-          <t>10- Inrush P/F</t>
-        </is>
-      </c>
-      <c r="BW1" s="6" t="inlineStr">
-        <is>
-          <t>10- Cont (A)</t>
-        </is>
-      </c>
-      <c r="BX1" s="6" t="inlineStr">
-        <is>
-          <t>10- Cont P/F</t>
-        </is>
-      </c>
-      <c r="BY1" s="6" t="inlineStr">
-        <is>
-          <t>10- Continuity</t>
-        </is>
-      </c>
-      <c r="BZ1" s="6" t="inlineStr">
-        <is>
-          <t>10- Release</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:BZ100000">

--- a/docs/Contactor_IQC_Sheet_Template.xlsx
+++ b/docs/Contactor_IQC_Sheet_Template.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -495,6 +495,7 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -558,6 +559,11 @@
           <t>Stagger (ms)</t>
         </is>
       </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>Continuity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -598,6 +604,11 @@
       <c r="L2" s="2" t="n">
         <v>1500</v>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -642,6 +653,11 @@
       <c r="L3" s="2" t="n">
         <v>1500</v>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -682,6 +698,11 @@
       <c r="L4" s="2" t="n">
         <v>1500</v>
       </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,7 +747,14 @@
       <c r="L5" s="2" t="n">
         <v>1500</v>
       </c>
-    </row>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -776,7 +804,19 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Continuity = Yes for 4-pin contactors (feedback contact wired to the rig): HMI shows CLOSE / OPEN. No = 2-pin, shows -NA-.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="M2:M9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/Contactor_IQC_Sheet_Template.xlsx
+++ b/docs/Contactor_IQC_Sheet_Template.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -559,11 +559,6 @@
           <t>Stagger (ms)</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
-        <is>
-          <t>Continuity</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -604,11 +599,6 @@
       <c r="L2" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -653,11 +643,6 @@
       <c r="L3" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -698,11 +683,6 @@
       <c r="L4" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,14 +727,7 @@
       <c r="L5" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
+    </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -804,19 +777,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Continuity = Yes for 4-pin contactors (feedback contact wired to the rig): HMI shows CLOSE / OPEN. No = 2-pin, shows -NA-.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="M2:M9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1025,7 +986,7 @@
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>1- Open</t>
+          <t>1- Contin. OFF</t>
         </is>
       </c>
       <c r="J1" s="6" t="inlineStr">
@@ -1050,7 +1011,7 @@
       </c>
       <c r="N1" s="6" t="inlineStr">
         <is>
-          <t>1- Continuity</t>
+          <t>1- Contin. ON</t>
         </is>
       </c>
       <c r="O1" s="6" t="inlineStr">
@@ -1060,7 +1021,7 @@
       </c>
       <c r="P1" s="6" t="inlineStr">
         <is>
-          <t>2- Open</t>
+          <t>2- Contin. OFF</t>
         </is>
       </c>
       <c r="Q1" s="6" t="inlineStr">
@@ -1085,7 +1046,7 @@
       </c>
       <c r="U1" s="6" t="inlineStr">
         <is>
-          <t>2- Continuity</t>
+          <t>2- Contin. ON</t>
         </is>
       </c>
       <c r="V1" s="6" t="inlineStr">
@@ -1095,7 +1056,7 @@
       </c>
       <c r="W1" s="6" t="inlineStr">
         <is>
-          <t>3- Open</t>
+          <t>3- Contin. OFF</t>
         </is>
       </c>
       <c r="X1" s="6" t="inlineStr">
@@ -1120,7 +1081,7 @@
       </c>
       <c r="AB1" s="6" t="inlineStr">
         <is>
-          <t>3- Continuity</t>
+          <t>3- Contin. ON</t>
         </is>
       </c>
       <c r="AC1" s="6" t="inlineStr">
@@ -1130,7 +1091,7 @@
       </c>
       <c r="AD1" s="6" t="inlineStr">
         <is>
-          <t>4- Open</t>
+          <t>4- Contin. OFF</t>
         </is>
       </c>
       <c r="AE1" s="6" t="inlineStr">
@@ -1155,7 +1116,7 @@
       </c>
       <c r="AI1" s="6" t="inlineStr">
         <is>
-          <t>4- Continuity</t>
+          <t>4- Contin. ON</t>
         </is>
       </c>
       <c r="AJ1" s="6" t="inlineStr">
@@ -1165,7 +1126,7 @@
       </c>
       <c r="AK1" s="6" t="inlineStr">
         <is>
-          <t>5- Open</t>
+          <t>5- Contin. OFF</t>
         </is>
       </c>
       <c r="AL1" s="6" t="inlineStr">
@@ -1190,7 +1151,7 @@
       </c>
       <c r="AP1" s="6" t="inlineStr">
         <is>
-          <t>5- Continuity</t>
+          <t>5- Contin. ON</t>
         </is>
       </c>
       <c r="AQ1" s="6" t="inlineStr">
@@ -1301,14 +1262,14 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Fail Step    step that failed, e.g. In-rush, Continuous current, Continuity, Release, Open</t>
+          <t xml:space="preserve">  Fail Step    step that failed, e.g. In-rush, Continuous current, Contin ON: OPEN, Contin OFF: CLOSE, Release: CLOSE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  n- ...       results of cycle n (Open, Inrush A, Inrush P/F, Cont A, Cont P/F, Continuity, Release)</t>
+          <t xml:space="preserve">  n- ...       results of cycle n (Contin. OFF, Inrush A, Inrush P/F, Cont A, Cont P/F, Contin. ON, Release)</t>
         </is>
       </c>
     </row>
